--- a/www/download/COUNTRY.BRA.rpA2.xlsx
+++ b/www/download/COUNTRY.BRA.rpA2.xlsx
@@ -342,7 +342,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AC37"/>
+  <dimension ref="A1:AC55"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -500,7 +500,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>Brasil</t>
         </is>
       </c>
     </row>
@@ -510,6 +510,11 @@
           <t>Computation method</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -847,2523 +852,4084 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>exchange.r.us</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.176</t>
+          <t>0.915734113517542</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.172</t>
+          <t>1.00469193759665</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.171</t>
+          <t>1.0775397229446</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>0.161</t>
+          <t>1.15970262026583</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>1.80401219237676</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.132</t>
+          <t>1.82715152306013</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>2.33426698569532</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.112</t>
+          <t>2.82845434464621</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>3.05819743146939</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.142</t>
+          <t>2.92039006162992</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>0.179</t>
+          <t>2.42365480933938</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.205</t>
+          <t>2.17533179323684</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>0.252</t>
+          <t>1.94704053129045</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.315</t>
+          <t>1.83376551466426</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>0.296</t>
+          <t>1.99942819729204</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Number of employee</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>surplus_value.empe_hs.r.pc</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>73.545</t>
+          <t>1.8904712464156</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>71.986</t>
+          <t>1.86217512751993</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>73.128</t>
+          <t>2.04994989574353</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>72.745</t>
+          <t>1.99754764722383</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>76.641</t>
+          <t>2.2269469242906</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>78.972</t>
+          <t>2.41198154831165</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>79.544</t>
+          <t>2.52904992169141</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>82.629</t>
+          <t>2.62186639074624</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>84.035</t>
+          <t>2.75649440314608</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>88.252</t>
+          <t>2.75637878948015</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>90.906</t>
+          <t>2.67701833981671</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>93.247</t>
+          <t>2.70366483536395</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>94.714</t>
+          <t>2.74633015450887</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>96.233</t>
+          <t>2.66460468392458</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>96.647</t>
+          <t>2.80401406324366</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>surplus_value.empe_ms.r.pc</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>59.052</t>
+          <t>2.51798939547118</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>57.777</t>
+          <t>2.60190433498542</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>58.432</t>
+          <t>2.88993931534211</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>57.853</t>
+          <t>2.94307483847319</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>60.702</t>
+          <t>3.40700908417507</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>62.692</t>
+          <t>3.59958853474558</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>63.064</t>
+          <t>3.82596372482122</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>65.474</t>
+          <t>4.12736971767109</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>66.734</t>
+          <t>4.27610153016007</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>70.286</t>
+          <t>4.20640368557213</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>72.221</t>
+          <t>4.08795786292191</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>73.868</t>
+          <t>4.04642946221457</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>74.771</t>
+          <t>4.02241329292071</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>75.799</t>
+          <t>3.84796722481591</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>76.071</t>
+          <t>3.96279691151319</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>surplus_value.empe_ls.r.pc</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>157522.872</t>
+          <t>3.38416836967617</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>154975.268</t>
+          <t>3.34252491508891</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>158449.89</t>
+          <t>3.51718590231625</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>158213.64</t>
+          <t>3.47127473779454</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>164642.11</t>
+          <t>3.93874183013134</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>170373.593</t>
+          <t>3.72214332976881</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>172038.194</t>
+          <t>3.8058343735742</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>179030.577</t>
+          <t>4.01851079758935</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>181564.871</t>
+          <t>3.93747791758987</t>
         </is>
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>189442.152</t>
+          <t>3.72049422077144</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>193103.106</t>
+          <t>3.45844325262886</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>197824.902</t>
+          <t>3.30022924360338</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>201071.541</t>
+          <t>3.15221634989529</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>204334.615</t>
+          <t>2.89739123052213</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
         <is>
-          <t>205284.27</t>
+          <t>2.83909759117874</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>gross_output.s.mv</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>124855.477</t>
+          <t>246012536586.712</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>122981.929</t>
+          <t>247352575559.412</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>125000.246</t>
+          <t>250239144641.097</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>124217.313</t>
+          <t>247947694876.928</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>128568.971</t>
+          <t>255990085203.73</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>133539.152</t>
+          <t>270756362498.075</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>134738.042</t>
+          <t>269842468798.575</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>140161.944</t>
+          <t>281113089318.648</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>142510.189</t>
+          <t>293683243610.161</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>149104.054</t>
+          <t>313037059054.32</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>151507.858</t>
+          <t>324853083647.284</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>154756.786</t>
+          <t>332808874680.622</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>156829.399</t>
+          <t>349565382208.736</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>159080.283</t>
+          <t>370920506554.364</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>159733.056</t>
+          <t>365185406085.193</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>labour_force_value.s.mv</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>28.53</t>
+          <t>64123450355.9119</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>28.91</t>
+          <t>64133688103.0367</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>29.29</t>
+          <t>62588347779.2225</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>29.66</t>
+          <t>63628023555.9015</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>30.04</t>
+          <t>60667839802.7095</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>30.42</t>
+          <t>63080440524.805</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>30.8</t>
+          <t>62838111748.2016</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>31.18</t>
+          <t>63422490827.4221</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>31.29</t>
+          <t>64451719637.9391</t>
         </is>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>31.41</t>
+          <t>69547971261.0647</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>31.52</t>
+          <t>74258638015.0628</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>31.97</t>
+          <t>79299164548.4806</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>32.43</t>
+          <t>83678446395.1372</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>32.88</t>
+          <t>90351677460.5981</t>
         </is>
       </c>
       <c r="Q14" t="inlineStr">
         <is>
-          <t>33.34</t>
+          <t>91228932186.1507</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>value.m.mv</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>30.28</t>
+          <t>6743426.84193174</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>30.81</t>
+          <t>6435737.98126827</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>31.33</t>
+          <t>6327250.63197218</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>31.85</t>
+          <t>6577034.27961869</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>32.38</t>
+          <t>9550073.10689473</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>32.9</t>
+          <t>8749974.06967635</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>10095979.0511817</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>33.95</t>
+          <t>11048107.5093815</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>34.78</t>
+          <t>10422929.6028786</t>
         </is>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>35.61</t>
+          <t>9309110.21573174</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>36.44</t>
+          <t>7707438.42660467</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>37.03</t>
+          <t>6652631.53359997</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>37.63</t>
+          <t>5627244.26728057</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>38.22</t>
+          <t>4908752.25141387</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
         <is>
-          <t>38.81</t>
+          <t>5232766.54249141</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>gdp.s.du</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>38.33</t>
+          <t>612928.381951027</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>37.43</t>
+          <t>603834.848648193</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>36.53</t>
+          <t>613176.524749872</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>35.62</t>
+          <t>606009.548177548</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>34.72</t>
+          <t>658386.950005693</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>33.82</t>
+          <t>685789.722159793</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>32.92</t>
+          <t>670628.416488916</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>32.01</t>
+          <t>705283.400436611</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>31.07</t>
+          <t>777993.382487165</t>
         </is>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>30.13</t>
+          <t>902770.03895177</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>29.18</t>
+          <t>994622.610324746</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>28.14</t>
+          <t>1075612.16251379</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>27.09</t>
+          <t>1272146.22816357</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>26.04</t>
+          <t>1467741.53498129</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>24.99</t>
+          <t>1371163.6747467</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>gross_output.s.du</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>29.41</t>
+          <t>1073143.42123088</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29.61</t>
+          <t>1075693.85196203</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>29.79</t>
+          <t>1070307.01610797</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>29.96</t>
+          <t>1047434.77834948</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>30.11</t>
+          <t>1115732.78585875</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>30.25</t>
+          <t>1186822.9968532</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>30.38</t>
+          <t>1141011.67057857</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>30.5</t>
+          <t>1203949.9090671</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>30.77</t>
+          <t>1346659.30812357</t>
         </is>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>31.02</t>
+          <t>1556843.80600535</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>31.25</t>
+          <t>1718465.44942581</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>32.37</t>
+          <t>1832357.68148712</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>33.42</t>
+          <t>2157562.89387592</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>34.42</t>
+          <t>2500907.3324096</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
         <is>
-          <t>35.36</t>
+          <t>2275853.98292366</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>surplus_value.empe.r.pc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>34.08</t>
+          <t>2.53668910932279</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>35.19</t>
+          <t>2.52936760201301</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>36.26</t>
+          <t>2.73757115953293</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>37.3</t>
+          <t>2.7076710724593</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>38.3</t>
+          <t>3.06273571738657</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>39.28</t>
+          <t>3.14966378109465</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>40.23</t>
+          <t>3.28443379682983</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>41.16</t>
+          <t>3.4657554688907</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>42.19</t>
+          <t>3.55119300854594</t>
         </is>
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>43.2</t>
+          <t>3.47720583481405</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>44.17</t>
+          <t>3.34113109398516</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>44.47</t>
+          <t>3.29370950727922</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>44.76</t>
+          <t>3.26551998283224</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>45.04</t>
+          <t>3.11336010639105</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
         <is>
-          <t>45.3</t>
+          <t>3.20175199506288</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>capital_depreciation.s.us</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>33.66</t>
+          <t>176456.739795647</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>32.35</t>
+          <t>171881.591541854</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>31.1</t>
+          <t>171384.406107029</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>29.89</t>
+          <t>160891.712033725</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>28.73</t>
+          <t>113760.958790005</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>27.61</t>
+          <t>131607.250077569</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>26.53</t>
+          <t>118662.525337633</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>25.49</t>
+          <t>112217.792776431</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>24.18</t>
+          <t>120483.288061918</t>
         </is>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>22.93</t>
+          <t>141621.64922617</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>21.72</t>
+          <t>179120.441546385</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>20.3</t>
+          <t>204740.203811757</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>18.96</t>
+          <t>252043.150529306</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>17.69</t>
+          <t>314590.733405019</t>
         </is>
       </c>
       <c r="Q19" t="inlineStr">
         <is>
-          <t>16.48</t>
+          <t>296158.785803693</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>labour_force_value.m.mv</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0.915734113517542</t>
+          <t>1085.8830225823</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.00469193759665</t>
+          <t>1110.02052592977</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1.0775397229446</t>
+          <t>1071.13515233392</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.15970262026583</t>
+          <t>1099.81759475178</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>1.80401219237676</t>
+          <t>999.441352128186</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1.82715152306013</t>
+          <t>1006.2012589157</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>2.33426698569532</t>
+          <t>996.411140685808</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.82845434464621</t>
+          <t>968.664955475235</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>3.05819743146939</t>
+          <t>965.805192413283</t>
         </is>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>2.92039006162992</t>
+          <t>989.500197412745</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>2.42365480933938</t>
+          <t>1028.20693361516</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2.17533179323684</t>
+          <t>1073.52349105962</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>1.94704053129045</t>
+          <t>1119.1303261863</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>1.83376551466426</t>
+          <t>1191.98819194508</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
         <is>
-          <t>1.99942819729204</t>
+          <t>1199.26480943081</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Value transfer through trade</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>trade_transfers.s.mv</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>0.328</t>
+          <t>4126613695.41893</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>7355541492.75579</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>5324186389.5862</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>0.354</t>
+          <t>7831983590.19931</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.243</t>
+          <t>-906535346.857638</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>1394748775.23088</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>0.226</t>
+          <t>-3001122170.27343</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.208</t>
+          <t>-4873237133.15394</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-3323226933.09564</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>0.261</t>
+          <t>-5387613544.72043</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>0.355</t>
+          <t>-1309061015.23086</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>0.446</t>
+          <t>3617646275.99113</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>0.565</t>
+          <t>6020891291.60431</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>0.691</t>
+          <t>8722491101.57042</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
         <is>
-          <t>0.707</t>
+          <t>4224360090.77645</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Value transfer through trade of productive sectors</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>trade_transfers.p.s.mv</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>0.357</t>
+          <t>5013966211.70021</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>0.386</t>
+          <t>8333506341.95348</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>0.383</t>
+          <t>6319727627.53862</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>0.374</t>
+          <t>8855658293.87656</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>0.256</t>
+          <t>-218223115.04241</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>0.278</t>
+          <t>2602204881.69485</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>-1632976540.14515</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>0.221</t>
+          <t>-4094326825.89622</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>0.232</t>
+          <t>-2537401380.8144</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>0.275</t>
+          <t>-4913817886.63184</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>0.375</t>
+          <t>-194940297.939234</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>0.473</t>
+          <t>4745112278.62693</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>0.695</t>
+          <t>7292478197.50655</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>0.837</t>
+          <t>10258299051.0316</t>
         </is>
       </c>
       <c r="Q22" t="inlineStr">
         <is>
-          <t>0.847</t>
+          <t>6938059105.90937</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Value transfer through trade of unproductive sectors</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>trade_transfers.u.s.mv</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2.658</t>
+          <t>-887352516.281275</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2.755</t>
+          <t>-977964849.197684</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2.787</t>
+          <t>-995541237.952425</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2.719</t>
+          <t>-1023674703.67725</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>-688312231.815228</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>2.116</t>
+          <t>-1207456106.46397</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.834</t>
+          <t>-1368145630.12828</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.768</t>
+          <t>-778910307.257726</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>1.809</t>
+          <t>-785825552.281243</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>2.085</t>
+          <t>-473795658.08859</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>2.611</t>
+          <t>-1114120717.29163</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2.933</t>
+          <t>-1127466002.6358</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>3.543</t>
+          <t>-1271586905.90224</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>4.244</t>
+          <t>-1535807949.46116</t>
         </is>
       </c>
       <c r="Q23" t="inlineStr">
         <is>
-          <t>4.228</t>
+          <t>-2713699015.13292</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Working day of employee per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>abstract_labour.empe.m.mv</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1.262</t>
+          <t>3840.43065996534</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>1.366</t>
+          <t>3917.67048178599</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1.421</t>
+          <t>4003.44385332516</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>4077.76188104293</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>4060.46607872431</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>1.097</t>
+          <t>4175.39692061432</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>0.948</t>
+          <t>4269.05756669204</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>0.898</t>
+          <t>4325.8208224363</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>0.979</t>
+          <t>4395.5658393287</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>4430.19605740599</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>1.562</t>
+          <t>4463.58109056792</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>1.895</t>
+          <t>4609.39801985025</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2.377</t>
+          <t>4773.67276974124</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>2.895</t>
+          <t>4903.07667603608</t>
         </is>
       </c>
       <c r="Q24" t="inlineStr">
         <is>
-          <t>2.741</t>
+          <t>5039.01330563461</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>abstract_labour.emp.m.mv</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>0.673</t>
+          <t>3927.78652638693</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>0.739</t>
+          <t>3997.7105495369</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>0.771</t>
+          <t>4088.80805956331</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>0.747</t>
+          <t>4166.40779093245</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>0.514</t>
+          <t>4159.13797887769</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>0.559</t>
+          <t>4262.38374311515</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>0.479</t>
+          <t>4351.75110171659</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>4402.4627436371</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>0.481</t>
+          <t>4471.63279926858</t>
         </is>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>0.571</t>
+          <t>4510.7698167236</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>4544.46506752615</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>0.935</t>
+          <t>4686.9179102621</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>1.175</t>
+          <t>4843.73723556415</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>1.407</t>
+          <t>4966.24963157692</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
         <is>
-          <t>1.398</t>
+          <t>5100.4245159669</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Total exports (USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>exports.s.us</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>189.05</t>
+          <t>55919.0744709033</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>186.22</t>
+          <t>55162.1956404715</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>204.99</t>
+          <t>59446.5520192967</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>199.75</t>
+          <t>58540.8818546665</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>222.69</t>
+          <t>55558.9445026074</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>241.2</t>
+          <t>64412.2788355735</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>252.9</t>
+          <t>67952.387212892</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>262.19</t>
+          <t>73652.5956675123</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>275.65</t>
+          <t>83307.2466443061</t>
         </is>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>275.64</t>
+          <t>109195.004740986</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>267.7</t>
+          <t>134029.798305241</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>270.37</t>
+          <t>156508.079884294</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>274.63</t>
+          <t>182673.133968401</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>266.46</t>
+          <t>225925.787330055</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
         <is>
-          <t>280.4</t>
+          <t>177168.145813593</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Total exports (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>exports.s.mv</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>251.8</t>
+          <t>15807454778.9658</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>260.19</t>
+          <t>15059824084.5087</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>288.99</t>
+          <t>16343850500.2326</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>294.31</t>
+          <t>15999023035.7694</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>340.7</t>
+          <t>21749976218.63</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>359.96</t>
+          <t>21171414758.0147</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>382.6</t>
+          <t>26506364561.9415</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>412.74</t>
+          <t>31009404935.6835</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>427.61</t>
+          <t>32377536991.1212</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>420.64</t>
+          <t>37293670794.8188</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>408.8</t>
+          <t>35477018228.515</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>404.64</t>
+          <t>34691668588.515</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>402.24</t>
+          <t>34280926577.5621</t>
         </is>
       </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>384.8</t>
+          <t>34878891141.3158</t>
         </is>
       </c>
       <c r="Q27" t="inlineStr">
         <is>
-          <t>396.28</t>
+          <t>31385336533.0746</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Total imports (USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>imports.s.us</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>338.42</t>
+          <t>63624.5740749555</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>334.25</t>
+          <t>66099.9739901101</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>351.72</t>
+          <t>73317.6085475123</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>347.13</t>
+          <t>70462.4594564374</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>393.87</t>
+          <t>60009.8886529971</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>372.21</t>
+          <t>71432.036347915</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>380.58</t>
+          <t>71207.593913016</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>401.85</t>
+          <t>62298.8280490103</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>393.75</t>
+          <t>63637.2100849141</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>372.05</t>
+          <t>79039.9726229725</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>345.84</t>
+          <t>96807.0042247079</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>330.02</t>
+          <t>118387.998731804</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>315.22</t>
+          <t>153431.634813008</t>
         </is>
       </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>289.74</t>
+          <t>211376.023931242</t>
         </is>
       </c>
       <c r="Q28" t="inlineStr">
         <is>
-          <t>283.91</t>
+          <t>168974.33912302</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Total imports (magnitude of value)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>imports.s.mv</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>288869.931</t>
+          <t>22149996315.7047</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>287777.774</t>
+          <t>25493905671.3446</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>299007.321</t>
+          <t>25299278360.0784</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>303084.755</t>
+          <t>27152405255.3736</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>318760.528</t>
+          <t>22131232953.7173</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>336610.448</t>
+          <t>24641380285.7824</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>346157.491</t>
+          <t>24524744511.7755</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>363771.389</t>
+          <t>22586513038.9992</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>375773.577</t>
+          <t>23230159047.1967</t>
         </is>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>398086.591</t>
+          <t>23627690292.5838</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>413117.655</t>
+          <t>24650756254.5717</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>437040.861</t>
+          <t>29351798743.3694</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>458769.288</t>
+          <t>34201546513.8507</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>477915.159</t>
+          <t>40856082986.0473</t>
         </is>
       </c>
       <c r="Q29" t="inlineStr">
         <is>
-          <t>492941.437</t>
+          <t>33885623018.1029</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Trade balance (USD)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>trade_balance.s.us</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>226784.709</t>
+          <t>-7705.49960405221</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>226351.361</t>
+          <t>-10937.7783496386</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>233928.404</t>
+          <t>-13871.0565282157</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>235911.782</t>
+          <t>-11921.5776017709</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>246477.4</t>
+          <t>-4450.94415038973</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>261762.619</t>
+          <t>-7019.75751234143</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>269225.73</t>
+          <t>-3255.20670012402</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>283229.335</t>
+          <t>11353.7676185021</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>293332.216</t>
+          <t>19670.036559392</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>311380.583</t>
+          <t>30155.0321180136</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>322366.482</t>
+          <t>37222.794080533</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>340487.577</t>
+          <t>38120.0811524903</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>356932.085</t>
+          <t>29241.4991553926</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>371648.986</t>
+          <t>14549.7633988127</t>
         </is>
       </c>
       <c r="Q30" t="inlineStr">
         <is>
-          <t>383321.348</t>
+          <t>8193.80669057303</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Trade balance (magnitude of value)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>trade_balance.s.mv</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>246012.537</t>
+          <t>-6342541536.73887</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>247352.576</t>
+          <t>-10434081586.8358</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>250239.145</t>
+          <t>-8955427859.84578</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>247947.695</t>
+          <t>-11153382219.6042</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>255990.085</t>
+          <t>-381256735.087265</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>270756.362</t>
+          <t>-3469965527.76775</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>269842.469</t>
+          <t>1981620050.16601</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>281113.089</t>
+          <t>8422891896.68434</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>293683.244</t>
+          <t>9147377943.92451</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>313037.059</t>
+          <t>13665980502.2349</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>324853.084</t>
+          <t>10826261973.9433</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>332808.875</t>
+          <t>5339869845.14563</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>349565.382</t>
+          <t>79380063.711455</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>370920.507</t>
+          <t>-5977191844.73145</t>
         </is>
       </c>
       <c r="Q31" t="inlineStr">
         <is>
-          <t>365185.406</t>
+          <t>-2500286485.02833</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>gdp.p.s.us</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>1.073</t>
+          <t>307826.44203</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>325696.19641</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>339814.34862</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>1.047</t>
+          <t>325817.53526</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>1.116</t>
+          <t>226786.80764</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>1.187</t>
+          <t>258213.76393</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>1.141</t>
+          <t>218486.14965</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1.204</t>
+          <t>207952.31113</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>1.347</t>
+          <t>227846.57867</t>
         </is>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>1.557</t>
+          <t>277971.10007</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>1.718</t>
+          <t>354224.1177</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>1.832</t>
+          <t>431003.88651</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>2.158</t>
+          <t>534472.07806</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>2.501</t>
+          <t>649810.03032</t>
         </is>
       </c>
       <c r="Q32" t="inlineStr">
         <is>
-          <t>2.276</t>
+          <t>630373.14299</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Rate of profit</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>appropriated_profit.r.pc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>140510.637</t>
+          <t>0.052243997889939</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>138850.013</t>
+          <t>0.065799993055667</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>143361.453</t>
+          <t>0.0776988822262481</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>143453.964</t>
+          <t>0.0778435962654476</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>151058.151</t>
+          <t>0.0763542861746593</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>156452.926</t>
+          <t>0.0704698143911199</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>158599.629</t>
+          <t>0.0658454504105279</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>164678.276</t>
+          <t>0.0661604297998362</t>
         </is>
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>169666.982</t>
+          <t>0.0710038395042892</t>
         </is>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>181521.407</t>
+          <t>0.0740190724686711</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>188020.203</t>
+          <t>0.0789540182471218</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>195362.116</t>
+          <t>0.087638324913398</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>206111.388</t>
+          <t>0.0643661972494932</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
         <is>
-          <t>217687.168</t>
+          <t>0.060265930537589</t>
         </is>
       </c>
       <c r="Q33" t="inlineStr">
         <is>
-          <t>220018.053</t>
+          <t>0.0602964293712051</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>compensation.empe.s.us</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>328022.217561222</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>0.604</t>
+          <t>357050.860492582</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>0.613</t>
+          <t>359800.07234588</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>0.606</t>
+          <t>354405.445036471</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>0.658</t>
+          <t>243070.117973706</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>0.686</t>
+          <t>261244.890042264</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.671</t>
+          <t>226361.85432922</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.705</t>
+          <t>208054.975411469</t>
         </is>
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>0.778</t>
+          <t>219695.42882029</t>
         </is>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>0.903</t>
+          <t>261347.622060217</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>0.995</t>
+          <t>355201.572591124</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>1.076</t>
+          <t>445629.031897406</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>1.272</t>
+          <t>564910.169945729</t>
         </is>
       </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>1.468</t>
+          <t>691295.03710285</t>
         </is>
       </c>
       <c r="Q34" t="inlineStr">
         <is>
-          <t>1.371</t>
+          <t>706701.547310895</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>compensation.emp.s.us</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>64123.45</t>
+          <t>357464.215007532</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>64133.688</t>
+          <t>386261.837240327</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62588.348</t>
+          <t>382909.754649366</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>63628.024</t>
+          <t>374196.607393886</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>60667.84</t>
+          <t>255838.859720888</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>63080.441</t>
+          <t>278432.354738735</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>62838.112</t>
+          <t>239810.05324894</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>63422.491</t>
+          <t>220899.745023004</t>
         </is>
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>64451.72</t>
+          <t>231929.903542001</t>
         </is>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>69547.971</t>
+          <t>274582.276132272</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>74258.638</t>
+          <t>374878.242364804</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>79299.165</t>
+          <t>473406.172577666</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>83678.446</t>
+          <t>694954.107433865</t>
         </is>
       </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>90351.677</t>
+          <t>836641.718047541</t>
         </is>
       </c>
       <c r="Q35" t="inlineStr">
         <is>
-          <t>91228.932</t>
+          <t>846505.046696694</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>capital_stock.s.us</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>253.67</t>
+          <t>2657544.91490704</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>252.94</t>
+          <t>2754537.28489732</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>273.76</t>
+          <t>2787196.46883731</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>270.77</t>
+          <t>2718929.34610389</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>306.27</t>
+          <t>1895367.49971133</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>314.97</t>
+          <t>2115917.71359179</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>328.44</t>
+          <t>1833706.71262236</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>346.58</t>
+          <t>1768386.41775049</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>355.12</t>
+          <t>1809238.63981075</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>347.72</t>
+          <t>2085356.56153879</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>334.11</t>
+          <t>2610569.13966916</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>329.37</t>
+          <t>2933384.85080145</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>326.55</t>
+          <t>3542955.74900728</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>311.34</t>
+          <t>4243999.76630099</t>
         </is>
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>320.18</t>
+          <t>4227866.28044271</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Total real wage (constant USD)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>compensation.emp.s.cu</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>6.743</t>
+          <t>357464.215007532</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>6.436</t>
+          <t>368611.060278216</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>6.327</t>
+          <t>367759.103557952</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>6.577</t>
+          <t>377762.247685968</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>9.55</t>
+          <t>371747.508532344</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>8.75</t>
+          <t>394993.174258897</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>10.096</t>
+          <t>395005.131467663</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>11.048</t>
+          <t>398454.12120389</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>10.423</t>
+          <t>399955.482576774</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>9.309</t>
+          <t>420381.380490107</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>7.707</t>
+          <t>441348.130864091</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>6.653</t>
+          <t>463664.07274651</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>5.627</t>
+          <t>570469.744645256</t>
         </is>
       </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>4.909</t>
+          <t>598485.341610338</t>
         </is>
       </c>
       <c r="Q37" t="inlineStr">
         <is>
-          <t>5.233</t>
+          <t>596660.920536902</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>328022.217561222</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>339770.95492785</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>344721.618845927</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>357115.059466346</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>352424.195876436</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>371020.318605678</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>372873.535863077</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>375221.962253843</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>378721.31730579</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>400969.203275503</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>418931.130914099</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>437298.196131812</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>461894.667202679</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>492391.934259925</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>496391.703197306</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>315297.510722468</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>353130.125759673</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>387946.456280634</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>372542.950326114</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>258480.391269112</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>280715.578621265</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>239403.76975106</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>229214.998226996</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>248946.178067999</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>295977.807677728</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>385235.365035196</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>461817.138462334</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>480089.739116135</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>570359.328522459</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>551084.026373306</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour (employee only)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>226784708525.954</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>226351360988.465</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>233928403582.439</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>235911782335.975</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>246477399663.155</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>261762619341.279</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>269225729702.965</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>283229335263.231</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>293332215804.951</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>311380582729.519</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>322366482484.178</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>340487576741.11</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>356932085230.814</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>371648985611.936</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>383321347820.615</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Hours of abstract labour</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>288869930534.43</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>287777774035.241</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>299007320950.987</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>303084754942.59</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>318760528292.589</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>336610448008.449</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>346157491259.901</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>363771389008.994</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>375773577325.512</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>398086591459.614</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>413117655388.456</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>437040860962.247</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>458769287749.135</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>477915158991.936</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>492941437153.661</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>140510637261.15</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>138850012718.052</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>143361453076.684</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>143453963578.339</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>151058150809.165</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>156452926091.656</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>158599628924.117</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>164678276104.962</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>169666981617.229</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>181521406903.966</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>188020202639.084</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>195362115713.39</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>206111387869.917</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>217687167609.526</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>220018053499.365</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Number of persons engaged</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>73545221.6136996</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>71985645.4011104</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>73128236.0519808</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>72744860.8372439</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>76641008.2837895</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>78972347</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>79544414</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>82629067</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>84034981</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>88252473</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>90905673</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>93246963</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr">
+        <is>
+          <t>94713909</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>96232609</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>96647139</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Number of employee</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>59051895.1142841</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>57777028.9872046</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>58431793.2642276</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>57853251.1750386</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>60701750.7065571</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>62691673.2272644</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>63064441.1552358</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>65474125.4640584</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>66733664.4534825</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>70285959.9653567</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>72221491.2069989</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>73868122.3176669</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr">
+        <is>
+          <t>74770957.8028244</t>
+        </is>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>75799138.0041801</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>76070715.5490115</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total hours worked by persons engaged</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>157522871815.931</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>154975267826.828</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>158449890428.51</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>158213639601.25</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>164642110208.336</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>170373593179.634</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>172038193512.572</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>179030577348.644</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>181564871488.186</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>189442152116.396</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>193103105662.399</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>197824901761.945</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr">
+        <is>
+          <t>201071540982.591</t>
+        </is>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>204334614712.513</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>205284270174.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total hours worked by employees</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>124855477356.272</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>122981929130.877</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>125000245608.597</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>124217313012.641</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>128568970516.355</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>133539151699.074</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>134738041576.624</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>140161944231.357</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>142510188701.274</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>149104053980.659</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>151507858121.156</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>154756786038.698</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr">
+        <is>
+          <t>156829398560.943</t>
+        </is>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>159080283416.758</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>159733056266.715</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Share of high-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0.28527207953238</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>0.289063672026907</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>0.292855264521435</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>0.296646857015962</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>0.30043844951049</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>0.304230042005017</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>0.308021634499545</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.311813226994072</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>0.312940804118395</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>0.314068381242717</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>0.31519595836704</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>0.319739582810603</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr">
+        <is>
+          <t>0.324283207254166</t>
+        </is>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>0.32882683169773</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>0.333370456141293</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Share of medium-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0.302847446399263</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>0.308080715976869</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>0.313313985554475</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>0.318547255132081</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>0.323780524709687</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>0.329013794287293</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>0.334247063864899</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.339480333442505</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>0.347788509864734</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>0.356096686286962</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>0.36440486270919</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>0.370335501013448</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr">
+        <is>
+          <t>0.376266139317706</t>
+        </is>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>0.382196777621964</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>0.388127415926222</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Share of low-skilled labour compensation</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0.383309045496929</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>0.374284183424795</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>0.365259321352662</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>0.356234459280528</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>0.347209597208395</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>0.338184735136261</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>0.329159873064128</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.320135010991994</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>0.310699257445443</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>0.301263503898892</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>0.291827750352342</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>0.28135348760452</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr">
+        <is>
+          <t>0.270879224856699</t>
+        </is>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>0.260404962108878</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>0.249930699361057</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>Share of hours worked by high-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0.29409052632085</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>0.296079227090833</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>0.297903785160528</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>0.299578526879231</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>0.301115664348116</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>0.302525690731196</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>0.303817683651494</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.304999541148803</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>0.307662199656366</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>0.310168322533745</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>0.312530559686387</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>0.323703354133469</t>
+        </is>
+      </c>
+      <c r="O50" t="inlineStr">
+        <is>
+          <t>0.334233478808998</t>
+        </is>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>0.344188726643852</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>0.353625231082756</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0.340784670955906</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>0.351855466310366</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>0.362574578195994</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>0.372962573399857</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>0.383038300726325</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>0.392819098775233</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>0.402320969988155</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.4115587281512</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>0.421928881883914</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>0.431953292642506</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>0.441650600042035</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>0.444694650255785</t>
+        </is>
+      </c>
+      <c r="O51" t="inlineStr">
+        <is>
+          <t>0.447591911401025</t>
+        </is>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>0.450352104408826</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>0.452984207244345</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>Share of hours worked by low-skilled persons engaged</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0.336553374151815</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>0.323493878027373</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>0.310950208072049</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>0.298887471149484</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>0.28727460635413</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>0.276083781922142</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>0.265289917788922</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.254870302128568</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>0.241837489888291</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>0.229306956252321</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>0.217247411700149</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>0.203030567039318</t>
+        </is>
+      </c>
+      <c r="O52" t="inlineStr">
+        <is>
+          <t>0.189603181218548</t>
+        </is>
+      </c>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>0.176887740375894</t>
+        </is>
+      </c>
+      <c r="Q52" t="inlineStr">
+        <is>
+          <t>0.164819133101471</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>Gross output (USD)</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>1261526.44119</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>1366247.23366</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>1420617.91803</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>1380365.38991</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>969896.04007</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>1096554.37795</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>948116.04885</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>897641.136</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>978595.75461</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>1175437.15757</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>1562385.44245</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>1895074.57938</t>
+        </is>
+      </c>
+      <c r="O53" t="inlineStr">
+        <is>
+          <t>2377320.84208</t>
+        </is>
+      </c>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>2894929.56407</t>
+        </is>
+      </c>
+      <c r="Q53" t="inlineStr">
+        <is>
+          <t>2741154.20109</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product (USD)</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>672761.72573</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>739391.963</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>770856.21093</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>746739.55772</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>514319.25099</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>559147.93336</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>479213.823</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>450114.74325</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>480876.08161</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>570560.08381</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>760113.6074</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>935223.31104</t>
+        </is>
+      </c>
+      <c r="O54" t="inlineStr">
+        <is>
+          <t>1175043.84655</t>
+        </is>
+      </c>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>1407001.04657</t>
+        </is>
+      </c>
+      <c r="Q54" t="inlineStr">
+        <is>
+          <t>1397589.07307</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>capital_stock.s.cu</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>2433604.55329256</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2496405.24300983</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>2573259.57977903</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2650481.85683378</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>2717570.77314825</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2799141.45096697</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>2886846.91913392</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>2963511.49594946</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>3029294.64737244</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>3121399.53784588</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>3243195.30579049</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>3429017.52373446</t>
+        </is>
+      </c>
+      <c r="O55" t="inlineStr">
+        <is>
+          <t>3675487.88361005</t>
+        </is>
+      </c>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>3959516.16837724</t>
+        </is>
+      </c>
+      <c r="Q55" t="inlineStr">
+        <is>
+          <t>4181401.4404286</t>
         </is>
       </c>
     </row>
@@ -3374,7 +4940,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C32"/>
+  <dimension ref="A1:C49"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3397,36 +4963,51 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Capital depreciation (USD)</t>
+          <t>Hours of abstract labour</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>capital_depreciation.s.us</t>
+          <t>abstract_labour.emp.s.mv</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Hours of abstract labour</t>
+          <t>Hours of abstract labour (employee only)</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>abstract_labour.emp.s.mv</t>
+          <t>abstract_labour.empe.s.mv</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Hours of abstract labour (employee only)</t>
+          <t>Number of persons engaged</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>abstract_labour.empe.s.mv</t>
+          <t>emp.s.un</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3438,331 +5019,695 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>emp.s.un</t>
+          <t>empe.s.un</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Number of persons engaged</t>
+          <t>Total hours worked by persons engaged</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>empe.s.un</t>
+          <t>hours_worked.emp.s.hr</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Total hours worked by persons engaged</t>
+          <t>Total hours worked by employees</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>hours_worked.emp.s.hr</t>
+          <t>hours_worked.empe.s.hr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Total hours worked by employees</t>
+          <t>Share of hours worked by high-skilled persons engaged</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>hours_worked.empe.s.hr</t>
+          <t>hours_worked.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Share of high-skilled labour compensation</t>
+          <t>Share of hours worked by medium-skilled persons engaged</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>compensation.empe_hs.r.pc</t>
+          <t>hours_worked.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Share of medium-skilled labour compensation</t>
+          <t>Share of hours worked by low-skilled persons engaged</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>compensation.empe_ms.r.pc</t>
+          <t>hours_worked.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Share of low-skilled labour compensation</t>
+          <t>Share of high-skilled labour compensation</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>compensation.empe_ls.r.pc</t>
+          <t>compensation.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Share of hours worked by high-skilled persons engaged</t>
+          <t>Share of medium-skilled labour compensation</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>hours_worked.empe_hs.r.pc</t>
+          <t>compensation.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Share of hours worked by medium-skilled persons engaged</t>
+          <t>Share of low-skilled labour compensation</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ms.r.pc</t>
+          <t>compensation.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Share of hours worked by low-skilled persons engaged</t>
+          <t>Compensation of employees (USD)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>hours_worked.empe_ls.r.pc</t>
+          <t>compensation.empe.s.us</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Exchange rate (USD)</t>
+          <t>Labour compensation (USD)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>exchange.r.us</t>
+          <t>compensation.emp.s.us</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Compensation of employees (USD)</t>
+          <t>Total labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>compensation.empe.s.us</t>
+          <t>labour_force_value.s.mv</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Labour compensation (USD)</t>
+          <t>Labour force value (magnitude of value)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>compensation.emp.s.us</t>
+          <t>labour_force_value.m.mv</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Capital stock (USD)</t>
+          <t>Capital depreciation (USD)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>capital_stock.s.us</t>
+          <t>capital_depreciation.s.us</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Gross output (USD)</t>
+          <t>Capital stock (USD)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>gross_output.s.us</t>
+          <t>capital_stock.s.us</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Gross output (magnitude of value)</t>
+          <t>Rate of surplus value</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>gross_output.s.mv</t>
+          <t>surplus_value.empe.r.pc</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Gross output (direct prices - USD)</t>
+          <t>Rate of surplus value of high-skilled employee</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>gross_output.s.du</t>
+          <t>surplus_value.empe_hs.r.pc</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Total labour force value (magnitude of value)</t>
+          <t>Rate of surplus value of medium-skilled employee</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>labour_force_value.s.mv</t>
+          <t>surplus_value.empe_ms.r.pc</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Rate of surplus value</t>
+          <t>Rate of surplus value of low-skilled employee</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>surplus_value.empe.r.pc</t>
+          <t>surplus_value.empe_ls.r.pc</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Rate of surplus value of high-skilled employee</t>
+          <t>Gross output (USD)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>surplus_value.empe_hs.r.pc</t>
+          <t>gross_output.s.us</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Rate of surplus value of medium-skilled employee</t>
+          <t>Gross output (magnitude of value)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ms.r.pc</t>
+          <t>gross_output.s.mv</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rate of surplus value of low-skilled employee</t>
+          <t>Gross output (direct prices - USD)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>surplus_value.empe_ls.r.pc</t>
+          <t>gross_output.s.du</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Complex labour multiplier</t>
+          <t>Gross Domestic Product (magnitude of value)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.emp.r.un</t>
+          <t>gdp.s.mv</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Complex labour multiplier (employee only)</t>
+          <t>Gross Domestic Product (direct prices - USD)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>complex_labour_multiplier.empe.r.un</t>
+          <t>gdp.s.du</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (magnitude of value)</t>
+          <t>Gross Domestic Product (USD)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>gdp.s.mv</t>
+          <t>gdp.s.us</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (direct prices - USD)</t>
+          <t>Value per output</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>gdp.s.du</t>
+          <t>value.m.mv</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Gross Domestic Product (USD)</t>
+          <t>Exchange rate (USD)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>gdp.s.us</t>
+          <t>exchange.r.us</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Value per output</t>
+          <t>Complex labour multiplier</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>value.m.mv</t>
+          <t>complex_labour_multiplier.emp.r.un</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Complex labour multiplier (employee only)</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>complex_labour_multiplier.empe.r.un</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>NaN</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Working day of employee per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>abstract_labour.empe.m.mv</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Magnitude of value "created" by employee in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>Working day of persons engaged per year (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>abstract_labour.emp.m.mv</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Magnitude of value created by persons engaged in each year. Includes productive and unproductive workers.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Total exports (USD)</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>exports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>Total exports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>exports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>Total imports (USD)</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>imports.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>Total imports (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>imports.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>Trade balance (USD)</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>trade_balance.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>Trade balance (magnitude of value)</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>trade_balance.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>Value transfer through trade</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>trade_transfers.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of productive sectors</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>trade_transfers.p.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>Value transfer through trade of unproductive sectors</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>trade_transfers.u.s.mv</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>Total real wage (constant USD)</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>compensation.emp.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>Total real compensation of labour (constant USD)</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>compensation.empe.s.cu</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>Gross Domestic Product of productive sectors (USD)</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>gdp.p.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>Total profit (USD)</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>profit.s.us</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>Rate of profit</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>appropriated_profit.r.pc</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>NaN</t>
         </is>
       </c>
     </row>
@@ -3799,6 +5744,11 @@
       </c>
     </row>
     <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Reduction Problem: Alternative 2</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>rpA2</t>
